--- a/GroceryApplicationProject/src/test/resources/TestData.xlsx
+++ b/GroceryApplicationProject/src/test/resources/TestData.xlsx
@@ -1,15 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C1E34F1-E059-4E64-AB2A-5DE660E5D0D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LoginPage" sheetId="1" r:id="rId1"/>
+    <sheet name="AdminSearch" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -19,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="5">
   <si>
     <t>admin</t>
   </si>
@@ -29,11 +32,17 @@
   <si>
     <t xml:space="preserve">local </t>
   </si>
+  <si>
+    <t>sample</t>
+  </si>
+  <si>
+    <t>staff</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -344,7 +353,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -383,4 +392,22 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE3D3435-AA40-4409-94B0-0104EDB9C3A0}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>